--- a/research/traditional_assets/database/data/tanzania/tanzania_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/tanzania/tanzania_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,41 +587,47 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.339</v>
+      </c>
+      <c r="E2">
+        <v>0.367</v>
+      </c>
       <c r="G2">
-        <v>0.5056451612903226</v>
+        <v>0.7232323232323233</v>
       </c>
       <c r="H2">
-        <v>0.5056451612903226</v>
+        <v>0.7232323232323233</v>
       </c>
       <c r="I2">
-        <v>1.096774193548387</v>
+        <v>0.7402020202020203</v>
       </c>
       <c r="J2">
-        <v>1.002971137521222</v>
+        <v>0.719523267789092</v>
       </c>
       <c r="K2">
-        <v>0.556</v>
+        <v>3.508</v>
       </c>
       <c r="L2">
-        <v>0.4483870967741936</v>
+        <v>0.7086868686868688</v>
       </c>
       <c r="M2">
-        <v>0.167</v>
+        <v>0.753</v>
       </c>
       <c r="N2">
-        <v>0.03436213991769548</v>
+        <v>0.0422085201793722</v>
       </c>
       <c r="O2">
-        <v>0.3003597122302158</v>
+        <v>0.2146522234891676</v>
       </c>
       <c r="P2">
-        <v>0.167</v>
+        <v>0.753</v>
       </c>
       <c r="Q2">
-        <v>0.03436213991769548</v>
+        <v>0.0422085201793722</v>
       </c>
       <c r="R2">
-        <v>0.3003597122302158</v>
+        <v>0.2146522234891676</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -630,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.6929999999999999</v>
+        <v>9.735000000000001</v>
       </c>
       <c r="V2">
-        <v>0.1425925925925926</v>
+        <v>0.5456838565022423</v>
       </c>
       <c r="W2">
-        <v>0.04920353982300885</v>
+        <v>0.08021048166900829</v>
       </c>
       <c r="X2">
-        <v>0.1413787687115297</v>
+        <v>0.1243809358521702</v>
       </c>
       <c r="Y2">
-        <v>-0.09217522888852087</v>
+        <v>-0.04417045418316194</v>
       </c>
       <c r="Z2">
-        <v>0.0998550491222419</v>
+        <v>0.1124667711812419</v>
       </c>
       <c r="AA2">
-        <v>0.1001517322053725</v>
+        <v>0.07841704343041028</v>
       </c>
       <c r="AB2">
-        <v>0.131003465485822</v>
+        <v>0.1095480213259072</v>
       </c>
       <c r="AC2">
-        <v>-0.03085173328044946</v>
+        <v>-0.03113097789549692</v>
       </c>
       <c r="AD2">
-        <v>1.18</v>
+        <v>10.229</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.18</v>
+        <v>10.229</v>
       </c>
       <c r="AG2">
-        <v>0.487</v>
+        <v>0.493999999999998</v>
       </c>
       <c r="AH2">
-        <v>0.195364238410596</v>
+        <v>0.3644233852292564</v>
       </c>
       <c r="AI2">
-        <v>0.09021406727828746</v>
+        <v>0.1471184685526902</v>
       </c>
       <c r="AJ2">
-        <v>0.0910791097811857</v>
+        <v>0.02694447474637275</v>
       </c>
       <c r="AK2">
-        <v>0.03931541131831759</v>
+        <v>0.008261698498177041</v>
       </c>
       <c r="AL2">
-        <v>0.175</v>
+        <v>0.16</v>
       </c>
       <c r="AM2">
-        <v>0.175</v>
+        <v>0.16</v>
       </c>
       <c r="AN2">
-        <v>0.8676470588235293</v>
+        <v>2.76758658008658</v>
       </c>
       <c r="AO2">
-        <v>7.771428571428572</v>
+        <v>22.9</v>
       </c>
       <c r="AP2">
-        <v>0.3580882352941176</v>
+        <v>0.1336580086580081</v>
       </c>
       <c r="AQ2">
-        <v>7.771428571428572</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TCCIA Investment PLC (DAR:TICL)</t>
+          <t>National Investment Company Limited (DAR:NICO)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -715,41 +721,47 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.339</v>
+      </c>
+      <c r="E3">
+        <v>0.367</v>
+      </c>
       <c r="G3">
-        <v>0.5056451612903226</v>
+        <v>0.7675070028011205</v>
       </c>
       <c r="H3">
-        <v>0.5056451612903226</v>
+        <v>0.7675070028011205</v>
       </c>
       <c r="I3">
-        <v>1.096774193548387</v>
+        <v>0.761904761904762</v>
       </c>
       <c r="J3">
-        <v>1.002971137521222</v>
+        <v>0.7280739161336177</v>
       </c>
       <c r="K3">
-        <v>0.556</v>
+        <v>2.56</v>
       </c>
       <c r="L3">
-        <v>0.4483870967741936</v>
+        <v>0.7170868347338936</v>
       </c>
       <c r="M3">
-        <v>0.167</v>
+        <v>0.478</v>
       </c>
       <c r="N3">
-        <v>0.03436213991769548</v>
+        <v>0.03886178861788617</v>
       </c>
       <c r="O3">
-        <v>0.3003597122302158</v>
+        <v>0.18671875</v>
       </c>
       <c r="P3">
-        <v>0.167</v>
+        <v>0.478</v>
       </c>
       <c r="Q3">
-        <v>0.03436213991769548</v>
+        <v>0.03886178861788617</v>
       </c>
       <c r="R3">
-        <v>0.3003597122302158</v>
+        <v>0.18671875</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,73 +770,201 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.6929999999999999</v>
+        <v>9.31</v>
       </c>
       <c r="V3">
-        <v>0.1425925925925926</v>
+        <v>0.7569105691056911</v>
       </c>
       <c r="W3">
-        <v>0.04920353982300885</v>
+        <v>0.08075709779179811</v>
       </c>
       <c r="X3">
-        <v>0.1413787687115297</v>
+        <v>0.1375113730495881</v>
       </c>
       <c r="Y3">
-        <v>-0.09217522888852087</v>
+        <v>-0.05675427525778996</v>
       </c>
       <c r="Z3">
-        <v>0.0998550491222419</v>
+        <v>0.1136146648844758</v>
       </c>
       <c r="AA3">
-        <v>0.1001517322053725</v>
+        <v>0.08271987399264895</v>
       </c>
       <c r="AB3">
-        <v>0.131003465485822</v>
+        <v>0.1125433401086673</v>
       </c>
       <c r="AC3">
-        <v>-0.03085173328044946</v>
+        <v>-0.02982346611601831</v>
       </c>
       <c r="AD3">
-        <v>1.18</v>
+        <v>9.27</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.18</v>
+        <v>9.27</v>
       </c>
       <c r="AG3">
-        <v>0.487</v>
+        <v>-0.04000000000000092</v>
       </c>
       <c r="AH3">
-        <v>0.195364238410596</v>
+        <v>0.4297635605006954</v>
       </c>
       <c r="AI3">
-        <v>0.09021406727828746</v>
+        <v>0.1720809355856692</v>
       </c>
       <c r="AJ3">
-        <v>0.0910791097811857</v>
+        <v>-0.003262642740619978</v>
       </c>
       <c r="AK3">
-        <v>0.03931541131831759</v>
+        <v>-0.0008976660682226418</v>
       </c>
       <c r="AL3">
-        <v>0.175</v>
+        <v>0.005</v>
       </c>
       <c r="AM3">
-        <v>0.175</v>
+        <v>0.005</v>
       </c>
       <c r="AN3">
-        <v>0.8676470588235293</v>
+        <v>3.383211678832116</v>
       </c>
       <c r="AO3">
-        <v>7.771428571428572</v>
+        <v>544</v>
       </c>
       <c r="AP3">
-        <v>0.3580882352941176</v>
+        <v>-0.01459854014598574</v>
       </c>
       <c r="AQ3">
-        <v>7.771428571428572</v>
+        <v>544</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Tanzania</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TCCIA Investment PLC (DAR:TICL)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="G4">
+        <v>0.6086956521739131</v>
+      </c>
+      <c r="H4">
+        <v>0.6086956521739131</v>
+      </c>
+      <c r="I4">
+        <v>0.6840579710144927</v>
+      </c>
+      <c r="J4">
+        <v>0.6762116334950355</v>
+      </c>
+      <c r="K4">
+        <v>0.948</v>
+      </c>
+      <c r="L4">
+        <v>0.6869565217391305</v>
+      </c>
+      <c r="M4">
+        <v>0.275</v>
+      </c>
+      <c r="N4">
+        <v>0.04963898916967509</v>
+      </c>
+      <c r="O4">
+        <v>0.290084388185654</v>
+      </c>
+      <c r="P4">
+        <v>0.275</v>
+      </c>
+      <c r="Q4">
+        <v>0.04963898916967509</v>
+      </c>
+      <c r="R4">
+        <v>0.290084388185654</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0.425</v>
+      </c>
+      <c r="V4">
+        <v>0.07671480144404332</v>
+      </c>
+      <c r="W4">
+        <v>0.07966386554621849</v>
+      </c>
+      <c r="X4">
+        <v>0.1112504986547524</v>
+      </c>
+      <c r="Y4">
+        <v>-0.03158663310853391</v>
+      </c>
+      <c r="Z4">
+        <v>0.1096020967357636</v>
+      </c>
+      <c r="AA4">
+        <v>0.07411421286817163</v>
+      </c>
+      <c r="AB4">
+        <v>0.1065527025431472</v>
+      </c>
+      <c r="AC4">
+        <v>-0.03243848967497553</v>
+      </c>
+      <c r="AD4">
+        <v>0.959</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0.959</v>
+      </c>
+      <c r="AG4">
+        <v>0.534</v>
+      </c>
+      <c r="AH4">
+        <v>0.1475611632558855</v>
+      </c>
+      <c r="AI4">
+        <v>0.06124273580688422</v>
+      </c>
+      <c r="AJ4">
+        <v>0.0879157062891011</v>
+      </c>
+      <c r="AK4">
+        <v>0.03505317053958251</v>
+      </c>
+      <c r="AL4">
+        <v>0.155</v>
+      </c>
+      <c r="AM4">
+        <v>0.155</v>
+      </c>
+      <c r="AN4">
+        <v>1.003138075313807</v>
+      </c>
+      <c r="AO4">
+        <v>6.090322580645161</v>
+      </c>
+      <c r="AP4">
+        <v>0.5585774058577406</v>
+      </c>
+      <c r="AQ4">
+        <v>6.090322580645161</v>
       </c>
     </row>
   </sheetData>
